--- a/MU/Test Evidance/CR 15.xlsx
+++ b/MU/Test Evidance/CR 15.xlsx
@@ -7,8 +7,14 @@
     <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
-    <sheet name="CR 15" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Crystallized data" sheetId="3" r:id="rId2"/>
+    <sheet name="update CG 1" sheetId="4" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'update CG 1'!$A$1:$K$49</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +33,199 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="80">
+  <si>
+    <t>MUDNEWM20262027C</t>
+  </si>
+  <si>
+    <t>custid</t>
+  </si>
+  <si>
+    <t>acctno</t>
+  </si>
+  <si>
+    <t>New CG sancamt</t>
+  </si>
+  <si>
+    <t>Update in base</t>
+  </si>
+  <si>
+    <t>Update in CP1</t>
+  </si>
+  <si>
+    <t>Status in CP1</t>
+  </si>
+  <si>
+    <t>Claim 1</t>
+  </si>
+  <si>
+    <t>Update in CP2</t>
+  </si>
+  <si>
+    <t>CR1501</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>CR1502</t>
+  </si>
+  <si>
+    <t>SND</t>
+  </si>
+  <si>
+    <t>CR1503</t>
+  </si>
+  <si>
+    <t>CR1504</t>
+  </si>
+  <si>
+    <t>CR1505</t>
+  </si>
+  <si>
+    <t>CR1506</t>
+  </si>
+  <si>
+    <t>CR1507</t>
+  </si>
+  <si>
+    <t>CR1508</t>
+  </si>
+  <si>
+    <t>CR1509</t>
+  </si>
+  <si>
+    <t>CR1510</t>
+  </si>
+  <si>
+    <t>CR1511</t>
+  </si>
+  <si>
+    <t>CR1512</t>
+  </si>
+  <si>
+    <t>CR1513</t>
+  </si>
+  <si>
+    <t>NPA</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>CR1514</t>
+  </si>
+  <si>
+    <t>CR1515</t>
+  </si>
+  <si>
+    <t>CR1516</t>
+  </si>
+  <si>
+    <t>CR1517</t>
+  </si>
+  <si>
+    <t>CR1518</t>
+  </si>
+  <si>
+    <t>CR1519</t>
+  </si>
+  <si>
+    <t>CR1520</t>
+  </si>
+  <si>
+    <t>CR1521</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>CR1522</t>
+  </si>
+  <si>
+    <t>CR1523</t>
+  </si>
+  <si>
+    <t>CR1524</t>
+  </si>
+  <si>
+    <t>Q2CR1501</t>
+  </si>
+  <si>
+    <t>Q2CR1502</t>
+  </si>
+  <si>
+    <t>Q2CR1503</t>
+  </si>
+  <si>
+    <t>Q2CR1504</t>
+  </si>
+  <si>
+    <t>Q2CR1505</t>
+  </si>
+  <si>
+    <t>Q2CR1506</t>
+  </si>
+  <si>
+    <t>Q2CR1507</t>
+  </si>
+  <si>
+    <t>Q2CR1508</t>
+  </si>
+  <si>
+    <t>Q2CR1509</t>
+  </si>
+  <si>
+    <t>Q2CR1510</t>
+  </si>
+  <si>
+    <t>Q2CR1511</t>
+  </si>
+  <si>
+    <t>Q2CR1512</t>
+  </si>
+  <si>
+    <t>Q2CR1513</t>
+  </si>
+  <si>
+    <t>Q2CR1514</t>
+  </si>
+  <si>
+    <t>Q2CR1515</t>
+  </si>
+  <si>
+    <t>Q2CR1516</t>
+  </si>
+  <si>
+    <t>Q2CR1517</t>
+  </si>
+  <si>
+    <t>Q2CR1518</t>
+  </si>
+  <si>
+    <t>Q2CR1519</t>
+  </si>
+  <si>
+    <t>Q2CR1520</t>
+  </si>
+  <si>
+    <t>Q2CR1521</t>
+  </si>
+  <si>
+    <t>Q2CR1522</t>
+  </si>
+  <si>
+    <t>Q2CR1523</t>
+  </si>
+  <si>
+    <t>Q2CR1524</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
   <si>
     <t>CustomersId</t>
   </si>
@@ -41,97 +239,40 @@
     <t>SanctionedDate_AsPerNewCG</t>
   </si>
   <si>
-    <t>LoanCategory</t>
-  </si>
-  <si>
-    <t>TypeOfLoan</t>
-  </si>
-  <si>
-    <t>IsMigrated</t>
+    <t>SanctionedLoanAmount_AsPerUpdateCG</t>
+  </si>
+  <si>
+    <t>SanctionedDate_AsPerUpdateCG</t>
+  </si>
+  <si>
+    <t>CloseStatus</t>
+  </si>
+  <si>
+    <t>ClosedDate</t>
   </si>
   <si>
     <t>CurrentPortfolioStatus</t>
   </si>
   <si>
-    <t>CR13Q1252602</t>
-  </si>
-  <si>
-    <t>MUDNEWM20252026C1</t>
-  </si>
-  <si>
-    <t>Self Help Group</t>
-  </si>
-  <si>
-    <t>Limit for Letter of Credit/Bank Guarantee</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>Currency Period 1</t>
-  </si>
-  <si>
-    <t>CR13Q1252604</t>
-  </si>
-  <si>
-    <t>MUDNEWM20252026C2</t>
-  </si>
-  <si>
-    <t>Limit for working capital (CC)</t>
-  </si>
-  <si>
-    <t>Q1SHG19</t>
-  </si>
-  <si>
-    <t>MUDNEWM20272028SHG1</t>
-  </si>
-  <si>
-    <t>Loan is Term Loan or Composite Loan (TL/CM)</t>
-  </si>
-  <si>
-    <t>Q1SHG282901</t>
-  </si>
-  <si>
-    <t>Q1SHG282902</t>
-  </si>
-  <si>
-    <t>Q1SHG282903</t>
-  </si>
-  <si>
-    <t>Q1SHG282904</t>
-  </si>
-  <si>
-    <t>Q1SHG282905</t>
-  </si>
-  <si>
-    <t>Q1SHG282906</t>
-  </si>
-  <si>
-    <t>Q1SHG282907</t>
-  </si>
-  <si>
-    <t>Q1SHG282908</t>
-  </si>
-  <si>
-    <t>Q1SHG282909</t>
-  </si>
-  <si>
-    <t>Q1SHG282910</t>
-  </si>
-  <si>
-    <t>Q1SHG282911</t>
-  </si>
-  <si>
-    <t>Q1SHG282912</t>
-  </si>
-  <si>
-    <t>Q1SHG282913</t>
-  </si>
-  <si>
-    <t>Q2SHG282901</t>
-  </si>
-  <si>
-    <t>Q2SHG282902</t>
+    <t>Crystallized</t>
+  </si>
+  <si>
+    <t>LoanAccountNpa</t>
+  </si>
+  <si>
+    <t>GuaranteeStatus</t>
+  </si>
+  <si>
+    <t>Guarantee Close By MLI</t>
+  </si>
+  <si>
+    <t>Currency Period 2</t>
+  </si>
+  <si>
+    <t>Guarantee(s) In Force</t>
+  </si>
+  <si>
+    <t>NPA Guarantee(s) In Force</t>
   </si>
 </sst>
 </file>
@@ -145,13 +286,20 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -161,10 +309,11 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -311,7 +460,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,7 +469,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -652,154 +819,181 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1333,522 +1527,4353 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="7"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.8571428571429" customWidth="1"/>
-    <col min="2" max="2" width="25.4285714285714" customWidth="1"/>
-    <col min="3" max="3" width="23.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="23.8571428571429" customWidth="1"/>
-    <col min="5" max="5" width="29.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="31.2857142857143" customWidth="1"/>
-    <col min="7" max="7" width="16.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="1" max="1" width="12.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="23.2857142857143" style="6" customWidth="1"/>
+    <col min="4" max="4" width="19.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="17.7142857142857" customWidth="1"/>
+    <col min="6" max="6" width="12.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="16.2857142857143" customWidth="1"/>
+    <col min="9" max="9" width="15.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A2" s="3" t="s">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" hidden="1" spans="1:9">
+      <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="D2" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="B3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="B4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E4" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D5" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E5" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="B6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D7" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E7" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D8" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E8" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D9" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E9" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E10" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D11" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E11" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D12" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E12" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D13" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E13" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" hidden="1" spans="1:9">
+      <c r="A14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D14" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E14" s="11">
+        <v>100000</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="11">
+        <v>100000</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" hidden="1" spans="1:9">
+      <c r="A15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D15" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E15" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" hidden="1" spans="1:9">
+      <c r="A16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D16" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E16" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" hidden="1" spans="1:9">
+      <c r="A17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D17" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E17" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" hidden="1" spans="1:9">
+      <c r="A18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D18" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E18" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" hidden="1" spans="1:9">
+      <c r="A19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E19" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" hidden="1" spans="1:9">
+      <c r="A20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D20" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E20" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" hidden="1" spans="1:9">
+      <c r="A21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D21" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E21" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" hidden="1" spans="1:9">
+      <c r="A22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" hidden="1" spans="1:9">
+      <c r="A23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E23" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="10">
+        <v>0</v>
+      </c>
+      <c r="I23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" hidden="1" spans="1:9">
+      <c r="A24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" hidden="1" spans="1:9">
+      <c r="A25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D25" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E25" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" hidden="1" spans="1:9">
+      <c r="A26" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="10">
+        <v>100000</v>
+      </c>
+      <c r="D26" s="10">
+        <v>100000</v>
+      </c>
+      <c r="E26" s="10">
+        <v>100000</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="10">
+        <v>100000</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="13">
+        <v>900000</v>
+      </c>
+      <c r="D27" s="13">
+        <v>900000</v>
+      </c>
+      <c r="E27" s="13">
+        <v>900000</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="13">
+        <v>900000</v>
+      </c>
+      <c r="I27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="15">
+        <v>800000</v>
+      </c>
+      <c r="D28" s="15">
+        <v>800000</v>
+      </c>
+      <c r="E28" s="15">
+        <v>800000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="15">
+        <v>800000</v>
+      </c>
+      <c r="I28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" hidden="1" spans="1:9">
+      <c r="A29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="15">
+        <v>500000</v>
+      </c>
+      <c r="D29" s="15">
+        <v>500000</v>
+      </c>
+      <c r="E29" s="15">
+        <v>500000</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="15">
+        <v>100000</v>
+      </c>
+      <c r="D30" s="15">
+        <v>100000</v>
+      </c>
+      <c r="E30" s="15">
+        <v>100000</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100000</v>
+      </c>
+      <c r="I30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" s="15">
+        <v>900000</v>
+      </c>
+      <c r="D31" s="15">
+        <v>900000</v>
+      </c>
+      <c r="E31" s="15">
+        <v>900000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="15">
+        <v>900000</v>
+      </c>
+      <c r="I31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" hidden="1" spans="1:9">
+      <c r="A32" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="15">
+        <v>800000</v>
+      </c>
+      <c r="D32" s="15">
+        <v>800000</v>
+      </c>
+      <c r="E32" s="15">
+        <v>800000</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="15">
+        <v>500000</v>
+      </c>
+      <c r="D33" s="15">
+        <v>500000</v>
+      </c>
+      <c r="E33" s="15">
+        <v>500000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="15">
+        <v>500000</v>
+      </c>
+      <c r="I33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="15">
+        <v>100000</v>
+      </c>
+      <c r="D34" s="15">
+        <v>100000</v>
+      </c>
+      <c r="E34" s="15">
+        <v>100000</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="15">
+        <v>100000</v>
+      </c>
+      <c r="I34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" hidden="1" spans="1:9">
+      <c r="A35" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="15">
+        <v>900000</v>
+      </c>
+      <c r="D35" s="15">
+        <v>900000</v>
+      </c>
+      <c r="E35" s="15">
+        <v>900000</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="15">
+        <v>800000</v>
+      </c>
+      <c r="D36" s="15">
+        <v>800000</v>
+      </c>
+      <c r="E36" s="15">
+        <v>800000</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="15">
+        <v>800000</v>
+      </c>
+      <c r="I36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="15">
+        <v>500000</v>
+      </c>
+      <c r="D37" s="15">
+        <v>500000</v>
+      </c>
+      <c r="E37" s="15">
+        <v>500000</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="15">
+        <v>500000</v>
+      </c>
+      <c r="I37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" hidden="1" spans="1:9">
+      <c r="A38" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="15">
+        <v>100000</v>
+      </c>
+      <c r="D38" s="15">
+        <v>100000</v>
+      </c>
+      <c r="E38" s="15">
+        <v>100000</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="15">
+        <v>900000</v>
+      </c>
+      <c r="D39" s="15">
+        <v>900000</v>
+      </c>
+      <c r="E39" s="15">
+        <v>900000</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="15">
+        <v>900000</v>
+      </c>
+      <c r="I39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="15">
+        <v>800000</v>
+      </c>
+      <c r="D40" s="15">
+        <v>800000</v>
+      </c>
+      <c r="E40" s="15">
+        <v>800000</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="15">
+        <v>800000</v>
+      </c>
+      <c r="I40" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" hidden="1" spans="1:9">
+      <c r="A41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="15">
+        <v>500000</v>
+      </c>
+      <c r="D41" s="15">
+        <v>500000</v>
+      </c>
+      <c r="E41" s="15">
+        <v>500000</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="15">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="15">
+        <v>100000</v>
+      </c>
+      <c r="D42" s="15">
+        <v>100000</v>
+      </c>
+      <c r="E42" s="15">
+        <v>100000</v>
+      </c>
+      <c r="F42" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="15">
+        <v>100000</v>
+      </c>
+      <c r="I42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="15">
+        <v>900000</v>
+      </c>
+      <c r="D43" s="15">
+        <v>900000</v>
+      </c>
+      <c r="E43" s="15">
+        <v>900000</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="15">
+        <v>900000</v>
+      </c>
+      <c r="I43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="16">
+        <v>1000000</v>
+      </c>
+      <c r="D44" s="16">
+        <v>1500000</v>
+      </c>
+      <c r="E44" s="16">
+        <v>1500000</v>
+      </c>
+      <c r="F44" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="16">
+        <v>1500000</v>
+      </c>
+      <c r="I44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="15">
+        <v>900000</v>
+      </c>
+      <c r="D45" s="15">
+        <v>900000</v>
+      </c>
+      <c r="E45" s="15">
+        <v>900000</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="15">
+        <v>900000</v>
+      </c>
+      <c r="I45" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="15">
+        <v>800000</v>
+      </c>
+      <c r="D46" s="15">
+        <v>800000</v>
+      </c>
+      <c r="E46" s="15">
+        <v>800000</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="15">
+        <v>800000</v>
+      </c>
+      <c r="I46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" s="15">
+        <v>500000</v>
+      </c>
+      <c r="D47" s="15">
+        <v>500000</v>
+      </c>
+      <c r="E47" s="15">
+        <v>500000</v>
+      </c>
+      <c r="F47" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="15">
+        <v>500000</v>
+      </c>
+      <c r="I47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48" s="15">
+        <v>100000</v>
+      </c>
+      <c r="D48" s="15">
+        <v>100000</v>
+      </c>
+      <c r="E48" s="15">
+        <v>100000</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="15">
+        <v>100000</v>
+      </c>
+      <c r="I48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="16">
+        <v>100000</v>
+      </c>
+      <c r="D49" s="16">
+        <v>100000</v>
+      </c>
+      <c r="E49" s="16">
+        <v>100000</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="16">
+        <v>100000</v>
+      </c>
+      <c r="I49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" hidden="1" spans="1:9">
+      <c r="A50" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="16">
+        <v>100000</v>
+      </c>
+      <c r="D50" s="16">
+        <v>100000</v>
+      </c>
+      <c r="E50" s="16">
+        <v>100000</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="15">
+        <v>2000001</v>
+      </c>
+      <c r="I50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:I50" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="SND"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I49"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.2857142857143" customWidth="1"/>
+    <col min="2" max="2" width="13.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="17.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="24.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="21.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="23.8571428571429" customWidth="1"/>
+    <col min="7" max="7" width="16.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="16.2857142857143" customWidth="1"/>
+    <col min="9" max="9" width="12.2857142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="5">
+        <v>46204</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E3" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E5" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A4" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3">
-        <v>1000</v>
-      </c>
-      <c r="D4" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E8" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A5" s="3" t="s">
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E9" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A6" s="3" t="s">
+      <c r="C10" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E10" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="D6" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A7" s="3" t="s">
+      <c r="C11" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E11" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="D7" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A8" s="3" t="s">
+      <c r="C12" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="D8" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A9" s="3" t="s">
+      <c r="C13" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E13" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C14" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D14" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E15" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D16" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E16" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F16" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D17" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E17" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D18" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E18" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E19" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F19" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D20" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E20" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D21" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E21" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D22" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D23" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D24" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D25" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F25" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D26" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E26" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D27" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E27" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D28" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E28" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D29" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E29" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D30" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E30" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D31" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E31" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D32" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E32" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D33" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D34" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E34" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D35" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E35" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D36" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E36" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D37" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E37" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D38" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D39" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E39" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D40" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E40" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D41" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E41" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E42" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="2">
         <v>1000000</v>
       </c>
-      <c r="D9" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1700000</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1800000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1000001</v>
-      </c>
-      <c r="D13" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="D14" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="3">
-        <v>10000</v>
-      </c>
-      <c r="D16" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="3">
-        <v>10000</v>
-      </c>
-      <c r="D17" s="4">
-        <v>46844</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="3">
-        <v>999999</v>
-      </c>
-      <c r="D18" s="4">
-        <v>46935</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="25.5" spans="1:8">
-      <c r="A19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="3">
-        <v>100</v>
-      </c>
-      <c r="D19" s="4">
-        <v>46935</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="C20" s="5">
-        <f>SUM(C2:C19)</f>
-        <v>15522105</v>
+      <c r="D43" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>46357</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E44" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D45" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E45" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D46" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E46" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D47" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E47" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E48" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D49" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E49" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K49"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="21.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="23.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="20.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="20.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="18.1428571428571" customWidth="1"/>
+    <col min="9" max="9" width="15.4285714285714" customWidth="1"/>
+    <col min="10" max="10" width="17.5714285714286" customWidth="1"/>
+    <col min="11" max="11" width="16.2857142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" ht="25.5" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="3">
+        <v>46204</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E3" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E4" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E5" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E8" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E9" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E10" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E11" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D12" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E12" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" ht="25.5" spans="1:11">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D13" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E13" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="3">
+        <v>46569</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" ht="25.5" spans="1:11">
+      <c r="A14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D14" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E14" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" ht="25.5" spans="1:11">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D15" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E15" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" ht="25.5" spans="1:11">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D16" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E16" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F16" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" ht="25.5" spans="1:11">
+      <c r="A17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D17" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E17" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" ht="25.5" spans="1:11">
+      <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D18" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E18" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" ht="25.5" spans="1:11">
+      <c r="A19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D19" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E19" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F19" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" ht="25.5" spans="1:11">
+      <c r="A20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D20" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E20" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" ht="25.5" spans="1:11">
+      <c r="A21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D21" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E21" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" ht="25.5" spans="1:11">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D22" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" ht="25.5" spans="1:11">
+      <c r="A23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D23" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E23" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" ht="25.5" spans="1:11">
+      <c r="A24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D24" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E24" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" ht="25.5" spans="1:11">
+      <c r="A25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D25" s="3">
+        <v>46113</v>
+      </c>
+      <c r="E25" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F25" s="3">
+        <v>46113</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D26" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E26" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D27" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E27" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D28" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E28" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D29" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E29" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D30" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E30" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D31" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E31" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D32" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E32" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D33" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E33" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D34" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E34" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D35" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E35" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D36" s="3">
+        <v>46204</v>
+      </c>
+      <c r="E36" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D37" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E37" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D38" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D39" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E39" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D40" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E40" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D41" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E41" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E42" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="D43" s="3">
+        <v>46235</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>46357</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2">
+        <v>900000</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E44" s="2">
+        <v>900000</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D45" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E45" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="2">
+        <v>500000</v>
+      </c>
+      <c r="D46" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E46" s="2">
+        <v>500000</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D47" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E47" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E48" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="2">
+        <v>100000</v>
+      </c>
+      <c r="D49" s="3">
+        <v>46244</v>
+      </c>
+      <c r="E49" s="2">
+        <v>100000</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K49" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>